--- a/modelos/Modelo_Base_Destinatarios.xlsx
+++ b/modelos/Modelo_Base_Destinatarios.xlsx
@@ -40,7 +40,7 @@
     <t>Pessoa Teste 1</t>
   </si>
   <si>
-    <t>luma.sampaio.dados@gmail.com</t>
+    <t/>
   </si>
   <si>
     <t>PARA</t>
